--- a/info.xlsx
+++ b/info.xlsx
@@ -1,182 +1,279 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="24000" windowHeight="9675"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="144525" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+  <si>
+    <t>来源</t>
+  </si>
+  <si>
+    <t>项目</t>
+  </si>
+  <si>
+    <t>电话</t>
+  </si>
+  <si>
+    <t>微信</t>
+  </si>
+  <si>
+    <t>省</t>
+  </si>
+  <si>
+    <t>城市</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>项目标签</t>
+  </si>
+  <si>
+    <t>校区</t>
+  </si>
+  <si>
+    <t>用户行为</t>
+  </si>
+  <si>
+    <t>row_id</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>税务师</t>
+  </si>
+  <si>
+    <t>19906919378</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>浙江省</t>
+  </si>
+  <si>
+    <t>杭州市</t>
+  </si>
+  <si>
+    <t>杭州封闭式税务师课程</t>
+  </si>
+  <si>
+    <t>网络营销/400来电</t>
+  </si>
+  <si>
+    <t>1777010563823</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="20">
-    <font>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
-    <fill>
-      <patternFill/>
+  <fills count="34">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -473,156 +570,160 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -678,74 +779,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -997,43 +1035,120 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <cols>
+    <col min="2" max="2" width="12.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.25" style="1" customWidth="1"/>
+    <col min="7" max="7" width="25.625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="23" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19.25" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="20.875" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/info.xlsx
+++ b/info.xlsx
@@ -67,28 +67,28 @@
     <t>400</t>
   </si>
   <si>
-    <t>税务师</t>
-  </si>
-  <si>
-    <t>19906919378</t>
+    <t>事业单位</t>
+  </si>
+  <si>
+    <t>15550819758</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>浙江省</t>
-  </si>
-  <si>
-    <t>杭州市</t>
-  </si>
-  <si>
-    <t>杭州封闭式税务师课程</t>
+    <t>上海市</t>
+  </si>
+  <si>
+    <t>直辖区</t>
+  </si>
+  <si>
+    <t>上海面试培训</t>
   </si>
   <si>
     <t>网络营销/400来电</t>
   </si>
   <si>
-    <t>1777010563823</t>
+    <t>1778574233523</t>
   </si>
 </sst>
 </file>

--- a/info.xlsx
+++ b/info.xlsx
@@ -1,270 +1,187 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24000" windowHeight="9675"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24000" windowHeight="9675" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
-  <si>
-    <t>来源</t>
-  </si>
-  <si>
-    <t>项目</t>
-  </si>
-  <si>
-    <t>电话</t>
-  </si>
-  <si>
-    <t>微信</t>
-  </si>
-  <si>
-    <t>省</t>
-  </si>
-  <si>
-    <t>城市</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>项目标签</t>
-  </si>
-  <si>
-    <t>校区</t>
-  </si>
-  <si>
-    <t>用户行为</t>
-  </si>
-  <si>
-    <t>row_id</t>
-  </si>
-  <si>
-    <t>400</t>
-  </si>
-  <si>
-    <t>事业单位</t>
-  </si>
-  <si>
-    <t>15550819758</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>上海市</t>
-  </si>
-  <si>
-    <t>直辖区</t>
-  </si>
-  <si>
-    <t>上海面试培训</t>
-  </si>
-  <si>
-    <t>网络营销/400来电</t>
-  </si>
-  <si>
-    <t>1778574233523</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="21">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <b val="1"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color theme="3"/>
       <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <b val="1"/>
       <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -570,160 +487,160 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -779,11 +696,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1035,120 +1015,162 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="2" max="2" width="12.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.25" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9.25" style="1" customWidth="1"/>
-    <col min="7" max="7" width="25.625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="23" style="1" customWidth="1"/>
-    <col min="9" max="9" width="19.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="20.875" style="1" customWidth="1"/>
+    <col width="12.375" customWidth="1" style="1" min="2" max="2"/>
+    <col width="14" customWidth="1" style="1" min="3" max="3"/>
+    <col width="13.25" customWidth="1" style="1" min="4" max="4"/>
+    <col width="10.75" customWidth="1" style="1" min="5" max="5"/>
+    <col width="9.25" customWidth="1" style="1" min="6" max="6"/>
+    <col width="25.625" customWidth="1" style="1" min="7" max="7"/>
+    <col width="23" customWidth="1" style="1" min="8" max="8"/>
+    <col width="19.25" customWidth="1" style="1" min="9" max="9"/>
+    <col width="17.125" customWidth="1" style="1" min="10" max="10"/>
+    <col width="20.875" customWidth="1" style="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>电话</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>微信</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>省</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>城市</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>项目标签</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>校区</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>用户行为</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>row_id</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" t="s">
-        <v>19</v>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>银行招聘考试</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>15803518299</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr"/>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>山西省</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>太原市</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>太原有没有银行系统的面试</t>
+        </is>
+      </c>
+      <c r="H2" s="0" t="inlineStr">
+        <is>
+          <t>银行招聘考试</t>
+        </is>
+      </c>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr">
+        <is>
+          <t>网络营销/400来电</t>
+        </is>
+      </c>
+      <c r="K2" s="0" t="inlineStr">
+        <is>
+          <t>1778662604009</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/info.xlsx
+++ b/info.xlsx
@@ -1100,36 +1100,36 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>银行招聘考试</t>
+          <t>雅思</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
         <is>
-          <t>15803518299</t>
+          <t>13353399093</t>
         </is>
       </c>
       <c r="D2" s="0" t="inlineStr"/>
       <c r="E2" s="0" t="inlineStr">
         <is>
-          <t>山西省</t>
+          <t>浙江省</t>
         </is>
       </c>
       <c r="F2" s="0" t="inlineStr">
         <is>
-          <t>太原市</t>
+          <t>温州市</t>
         </is>
       </c>
       <c r="G2" s="0" t="inlineStr">
         <is>
-          <t>太原有没有银行系统的面试</t>
-        </is>
-      </c>
-      <c r="H2" s="0" t="inlineStr">
-        <is>
-          <t>银行招聘考试</t>
-        </is>
-      </c>
-      <c r="I2" s="0" t="inlineStr"/>
+          <t>雅思，价格多少</t>
+        </is>
+      </c>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr">
+        <is>
+          <t>高顿网校 SEO</t>
+        </is>
+      </c>
       <c r="J2" s="0" t="inlineStr">
         <is>
           <t>网络营销/400来电</t>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="K2" s="0" t="inlineStr">
         <is>
-          <t>1778662604009</t>
+          <t>1778725873038</t>
         </is>
       </c>
     </row>

--- a/info.xlsx
+++ b/info.xlsx
@@ -1100,31 +1100,35 @@
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t>雅思</t>
+          <t>银行招聘考试</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
         <is>
-          <t>13353399093</t>
+          <t>13853490366</t>
         </is>
       </c>
       <c r="D2" s="0" t="inlineStr"/>
       <c r="E2" s="0" t="inlineStr">
         <is>
-          <t>浙江省</t>
+          <t>山东省</t>
         </is>
       </c>
       <c r="F2" s="0" t="inlineStr">
         <is>
-          <t>温州市</t>
+          <t>德州市</t>
         </is>
       </c>
       <c r="G2" s="0" t="inlineStr">
         <is>
-          <t>雅思，价格多少</t>
-        </is>
-      </c>
-      <c r="H2" s="0" t="inlineStr"/>
+          <t>秋季考银行</t>
+        </is>
+      </c>
+      <c r="H2" s="0" t="inlineStr">
+        <is>
+          <t>银行招聘考试</t>
+        </is>
+      </c>
       <c r="I2" s="0" t="inlineStr">
         <is>
           <t>高顿网校 SEO</t>
@@ -1137,7 +1141,7 @@
       </c>
       <c r="K2" s="0" t="inlineStr">
         <is>
-          <t>1778725873038</t>
+          <t>1778729472461</t>
         </is>
       </c>
     </row>

--- a/info.xlsx
+++ b/info.xlsx
@@ -1105,23 +1105,23 @@
       </c>
       <c r="C2" s="0" t="inlineStr">
         <is>
-          <t>13853490366</t>
+          <t>13751827243</t>
         </is>
       </c>
       <c r="D2" s="0" t="inlineStr"/>
       <c r="E2" s="0" t="inlineStr">
         <is>
-          <t>山东省</t>
+          <t>广东省</t>
         </is>
       </c>
       <c r="F2" s="0" t="inlineStr">
         <is>
-          <t>德州市</t>
+          <t>广州市</t>
         </is>
       </c>
       <c r="G2" s="0" t="inlineStr">
         <is>
-          <t>秋季考银行</t>
+          <t>银行面试，线下班</t>
         </is>
       </c>
       <c r="H2" s="0" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="K2" s="0" t="inlineStr">
         <is>
-          <t>1778729472461</t>
+          <t>1778810474160</t>
         </is>
       </c>
     </row>
